--- a/Aeterna dokumentációk/LOOKUPS v2.xlsx
+++ b/Aeterna dokumentációk/LOOKUPS v2.xlsx
@@ -35,182 +35,188 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
+  <si>
+    <t>change_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>change_date</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>record_id</t>
+  </si>
+  <si>
+    <t>change_type</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>decision_id</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>table_id</t>
+  </si>
+  <si>
+    <t>export_enabled</t>
+  </si>
+  <si>
+    <t>output_name</t>
+  </si>
+  <si>
+    <t>record_type</t>
+  </si>
+  <si>
+    <t>output_format</t>
+  </si>
+  <si>
+    <t>schema_version</t>
+  </si>
+  <si>
+    <t>load_order</t>
+  </si>
+  <si>
+    <t>primary_key</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>field_id</t>
+  </si>
+  <si>
+    <t>group_kind</t>
+  </si>
+  <si>
+    <t>value_data_type</t>
+  </si>
+  <si>
+    <t>multi_select_allowed</t>
+  </si>
+  <si>
+    <t>field_name</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>column_order</t>
+  </si>
+  <si>
+    <t>default_rules_layer</t>
+  </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>runtime_enabled</t>
+  </si>
+  <si>
+    <t>required_mode</t>
+  </si>
+  <si>
+    <t>nullable</t>
+  </si>
+  <si>
+    <t>allowed_group_id</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>reference_table_id</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
+    <t>reference_field_id</t>
+  </si>
+  <si>
+    <t>default_value</t>
+  </si>
+  <si>
+    <t>registry_value_id</t>
+  </si>
+  <si>
+    <t>value_id</t>
+  </si>
+  <si>
+    <t>lifecycle_status</t>
+  </si>
+  <si>
+    <t>rules_layer</t>
+  </si>
+  <si>
+    <t>engine_support_status</t>
+  </si>
+  <si>
+    <t>introduced_in</t>
+  </si>
+  <si>
+    <t>deprecated_in</t>
+  </si>
+  <si>
+    <t>relation_id</t>
+  </si>
+  <si>
+    <t>source_registry_value_id</t>
+  </si>
+  <si>
+    <t>relation_type_id</t>
+  </si>
+  <si>
+    <t>target_registry_value_id</t>
+  </si>
+  <si>
+    <t>qualifier</t>
+  </si>
+  <si>
+    <t>alias_id</t>
+  </si>
+  <si>
+    <t>alias_value</t>
+  </si>
+  <si>
+    <t>canonical_registry_value_id</t>
+  </si>
+  <si>
+    <t>alias_type</t>
+  </si>
+  <si>
+    <t>normalization_mode</t>
+  </si>
+  <si>
+    <t>case_sensitive</t>
+  </si>
+  <si>
+    <t>requires_audit</t>
+  </si>
   <si>
     <t>key</t>
   </si>
   <si>
-    <t>change_id</t>
-  </si>
-  <si>
-    <t>sheet_name</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>export_enabled</t>
-  </si>
-  <si>
-    <t>change_date</t>
-  </si>
-  <si>
-    <t>output_name</t>
-  </si>
-  <si>
     <t>value_type</t>
   </si>
   <si>
-    <t>output_format</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>record_id</t>
-  </si>
-  <si>
-    <t>record_type</t>
-  </si>
-  <si>
-    <t>change_type</t>
-  </si>
-  <si>
-    <t>schema_version</t>
-  </si>
-  <si>
-    <t>summary</t>
-  </si>
-  <si>
-    <t>primary_key</t>
-  </si>
-  <si>
-    <t>decision_id</t>
-  </si>
-  <si>
-    <t>load_order</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>table_id</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>field_id</t>
-  </si>
-  <si>
-    <t>field_name</t>
-  </si>
-  <si>
-    <t>column_order</t>
-  </si>
-  <si>
-    <t>data_type</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>nullable</t>
-  </si>
-  <si>
-    <t>reference_table_id</t>
-  </si>
-  <si>
-    <t>reference_field</t>
-  </si>
-  <si>
-    <t>default_value</t>
-  </si>
-  <si>
-    <t>group_id</t>
-  </si>
-  <si>
-    <t>group_kind</t>
-  </si>
-  <si>
-    <t>value_data_type</t>
-  </si>
-  <si>
-    <t>relation_id</t>
-  </si>
-  <si>
-    <t>registry_value_id</t>
-  </si>
-  <si>
-    <t>source_registry_value_id</t>
-  </si>
-  <si>
-    <t>relation_type_id</t>
-  </si>
-  <si>
-    <t>target_registry_value_id</t>
-  </si>
-  <si>
-    <t>value_id</t>
-  </si>
-  <si>
-    <t>qualifier</t>
-  </si>
-  <si>
-    <t>lifecycle_status</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>rules_layer</t>
-  </si>
-  <si>
-    <t>sort_order</t>
-  </si>
-  <si>
-    <t>multi_select_allowed</t>
-  </si>
-  <si>
-    <t>runtime_enabled</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>engine_support_status</t>
-  </si>
-  <si>
-    <t>introduced_in</t>
-  </si>
-  <si>
-    <t>deprecated_in</t>
-  </si>
-  <si>
-    <t>alias_id</t>
-  </si>
-  <si>
-    <t>alias_value</t>
-  </si>
-  <si>
-    <t>canonical_value_id</t>
-  </si>
-  <si>
-    <t>alias_type</t>
-  </si>
-  <si>
-    <t>normalization_mode</t>
-  </si>
-  <si>
-    <t>case_sensitive</t>
-  </si>
-  <si>
-    <t>requires_audit</t>
-  </si>
-  <si>
     <t>localization_id</t>
   </si>
   <si>
@@ -283,54 +289,54 @@
     <t>operator_id</t>
   </si>
   <si>
+    <t>operator_kind</t>
+  </si>
+  <si>
+    <t>operand_type</t>
+  </si>
+  <si>
+    <t>arity</t>
+  </si>
+  <si>
+    <t>supports_null</t>
+  </si>
+  <si>
+    <t>supports_collection</t>
+  </si>
+  <si>
+    <t>precedence</t>
+  </si>
+  <si>
+    <t>engine_token</t>
+  </si>
+  <si>
     <t>target_primitive_id</t>
   </si>
   <si>
-    <t>operator_kind</t>
-  </si>
-  <si>
     <t>target_kind</t>
   </si>
   <si>
     <t>result_type</t>
   </si>
   <si>
-    <t>operand_type</t>
-  </si>
-  <si>
     <t>parameter_schema_id</t>
   </si>
   <si>
-    <t>arity</t>
+    <t>cost_component_type_id</t>
   </si>
   <si>
     <t>selection_required</t>
   </si>
   <si>
-    <t>supports_null</t>
+    <t>component_kind</t>
   </si>
   <si>
     <t>supports_count</t>
   </si>
   <si>
-    <t>supports_collection</t>
-  </si>
-  <si>
     <t>supports_filters</t>
   </si>
   <si>
-    <t>precedence</t>
-  </si>
-  <si>
-    <t>engine_token</t>
-  </si>
-  <si>
-    <t>cost_component_type_id</t>
-  </si>
-  <si>
-    <t>component_kind</t>
-  </si>
-  <si>
     <t>resource_group_id</t>
   </si>
   <si>
@@ -466,13 +472,25 @@
     <t>comparison_value</t>
   </si>
   <si>
+    <t>source_kind</t>
+  </si>
+  <si>
+    <t>authority_level</t>
+  </si>
+  <si>
     <t>minimum_value</t>
   </si>
   <si>
     <t>maximum_value</t>
   </si>
   <si>
-    <t>reference_field_id</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>path_or_uri</t>
+  </si>
+  <si>
+    <t>section</t>
   </si>
   <si>
     <t>severity</t>
@@ -481,31 +499,16 @@
     <t>error_code</t>
   </si>
   <si>
+    <t>supersedes_source_id</t>
+  </si>
+  <si>
     <t>message_key</t>
   </si>
   <si>
+    <t>checksum</t>
+  </si>
+  <si>
     <t>validation_stage</t>
-  </si>
-  <si>
-    <t>source_kind</t>
-  </si>
-  <si>
-    <t>authority_level</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>path_or_uri</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>supersedes_source_id</t>
-  </si>
-  <si>
-    <t>checksum</t>
   </si>
   <si>
     <t>migration_id</t>
@@ -891,16 +894,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -917,34 +920,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -965,34 +968,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1014,34 +1017,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1063,34 +1066,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
+      <c r="E1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1111,40 +1114,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1167,37 +1170,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1220,34 +1223,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
+      <c r="E1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1275,52 +1278,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1343,34 +1346,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1395,28 +1398,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1433,31 +1436,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1482,37 +1485,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1534,37 +1537,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>132</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1588,31 +1591,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1638,58 +1641,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>142</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1709,37 +1712,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>156</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1762,49 +1765,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>138</v>
+      <c r="F1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1824,119 +1827,117 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="13.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="8" max="9" width="14.88"/>
+    <col customWidth="1" min="10" max="10" width="14.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="8" max="8" width="14.88"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1953,42 +1954,43 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="13.25"/>
     <col customWidth="1" min="4" max="4" width="16.5"/>
+    <col customWidth="1" min="6" max="6" width="15.13"/>
     <col customWidth="1" min="7" max="7" width="13.5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2019,40 +2021,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2073,31 +2075,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2112,43 +2114,43 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="15.25"/>
+    <col customWidth="1" min="4" max="4" width="21.63"/>
     <col customWidth="1" min="6" max="6" width="16.13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
